--- a/LoanOfficer-A/2026/179 lanchenbi ayanpalli - samila.xlsx
+++ b/LoanOfficer-A/2026/179 lanchenbi ayanpalli - samila.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="K1" s="15">
         <f>17-K2</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="11"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="O1" s="12">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>15400</v>
+        <v>16800</v>
       </c>
       <c r="P1" s="16"/>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="K2" s="15">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="11"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="O2" s="18">
         <f>C2-O1</f>
-        <v>8400</v>
+        <v>7000</v>
       </c>
       <c r="P2" s="16"/>
     </row>
@@ -1236,9 +1236,15 @@
       <c r="A14" s="20">
         <v>12</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="21">
+        <v>46178</v>
+      </c>
+      <c r="C14" s="22">
+        <v>1400</v>
+      </c>
+      <c r="D14" s="20">
+        <v>1</v>
+      </c>
       <c r="E14" s="20">
         <v>42</v>
       </c>
